--- a/file/temp/class/DAPC_ProyectoCAD_2025_02_Grupo4.xlsx
+++ b/file/temp/class/DAPC_ProyectoCAD_2025_02_Grupo4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\temp\class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3581C94E-E1D3-44EB-BCED-B22EB009A9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B58118-0DF8-4EE6-9C75-9F99FD5AAE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="709" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -805,7 +805,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="575">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -2728,6 +2728,15 @@
   </si>
   <si>
     <t>Opcional en pdf.</t>
+  </si>
+  <si>
+    <t>Puertas, ventanas en vista de alzado.</t>
+  </si>
+  <si>
+    <t>Esquema</t>
+  </si>
+  <si>
+    <t>No calculado.</t>
   </si>
 </sst>
 </file>
@@ -3425,7 +3434,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3938,18 +3947,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3957,6 +3954,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3971,6 +3977,16 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -3983,24 +3999,8 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4020,6 +4020,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4058,6 +4067,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4789,100 +4802,100 @@
       </c>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="169" t="s">
+      <c r="B2" s="182" t="s">
         <v>467</v>
       </c>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
       <c r="E2" s="109"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="191" t="s">
         <v>371</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
       <c r="E3" s="108"/>
     </row>
     <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
       <c r="E4" s="107"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
+      <c r="B5" s="189"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="189"/>
       <c r="E5" s="107"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="168"/>
-      <c r="C6" s="168"/>
-      <c r="D6" s="168"/>
+      <c r="B6" s="190"/>
+      <c r="C6" s="190"/>
+      <c r="D6" s="190"/>
       <c r="E6" s="107"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="180" t="s">
+      <c r="B7" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="181"/>
-      <c r="D7" s="181"/>
-      <c r="E7" s="182"/>
+      <c r="C7" s="171"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="172"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="174">
+      <c r="B8" s="173">
         <v>4</v>
       </c>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="176"/>
+      <c r="C8" s="174"/>
+      <c r="D8" s="174"/>
+      <c r="E8" s="175"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="171" t="s">
+      <c r="B9" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="172"/>
-      <c r="D9" s="172"/>
-      <c r="E9" s="173"/>
+      <c r="C9" s="168"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="169"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="174" t="s">
+      <c r="B10" s="173" t="s">
         <v>495</v>
       </c>
-      <c r="C10" s="175"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="176"/>
+      <c r="C10" s="174"/>
+      <c r="D10" s="174"/>
+      <c r="E10" s="175"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="177"/>
-      <c r="C11" s="178"/>
-      <c r="D11" s="178"/>
-      <c r="E11" s="179"/>
+      <c r="B11" s="179"/>
+      <c r="C11" s="180"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="181"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="171" t="s">
+      <c r="B12" s="167" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="172"/>
-      <c r="D12" s="172"/>
-      <c r="E12" s="173"/>
+      <c r="C12" s="168"/>
+      <c r="D12" s="168"/>
+      <c r="E12" s="169"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="185" t="s">
+      <c r="B13" s="178" t="s">
         <v>496</v>
       </c>
-      <c r="C13" s="175"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="176"/>
+      <c r="C13" s="174"/>
+      <c r="D13" s="174"/>
+      <c r="E13" s="175"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="177"/>
-      <c r="C14" s="178"/>
-      <c r="D14" s="178"/>
-      <c r="E14" s="179"/>
+      <c r="B14" s="179"/>
+      <c r="C14" s="180"/>
+      <c r="D14" s="180"/>
+      <c r="E14" s="181"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="64" t="s">
@@ -4905,12 +4918,12 @@
       <c r="I16" s="85"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="169" t="s">
+      <c r="B17" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="169"/>
-      <c r="D17" s="169"/>
-      <c r="E17" s="169"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+      <c r="E17" s="182"/>
       <c r="G17" s="143">
         <v>0.3</v>
       </c>
@@ -4958,14 +4971,14 @@
       </c>
       <c r="G19" s="149">
         <f>$E$39</f>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H19" s="150">
         <v>0</v>
       </c>
       <c r="I19" s="151">
         <f>G19*$G$17+H19*$H$17</f>
-        <v>1.1604999999999999</v>
+        <v>1.2564000000000002</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
@@ -4984,14 +4997,14 @@
       </c>
       <c r="G20" s="149">
         <f t="shared" ref="G20:G28" si="1">$E$39</f>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H20" s="150">
         <v>4.7</v>
       </c>
       <c r="I20" s="151">
         <f t="shared" ref="I20:I28" si="2">G20*$G$17+H20*$H$17</f>
-        <v>4.4504999999999999</v>
+        <v>4.5464000000000002</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
@@ -5010,14 +5023,14 @@
       </c>
       <c r="G21" s="149">
         <f t="shared" si="1"/>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H21" s="150">
         <v>5</v>
       </c>
       <c r="I21" s="151">
         <f t="shared" si="2"/>
-        <v>4.6604999999999999</v>
+        <v>4.7564000000000002</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
@@ -5036,14 +5049,14 @@
       </c>
       <c r="G22" s="149">
         <f t="shared" si="1"/>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H22" s="150">
         <v>5</v>
       </c>
       <c r="I22" s="151">
         <f t="shared" si="2"/>
-        <v>4.6604999999999999</v>
+        <v>4.7564000000000002</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
@@ -5062,14 +5075,14 @@
       </c>
       <c r="G23" s="149">
         <f t="shared" si="1"/>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H23" s="150">
         <v>5</v>
       </c>
       <c r="I23" s="151">
         <f t="shared" si="2"/>
-        <v>4.6604999999999999</v>
+        <v>4.7564000000000002</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
@@ -5088,14 +5101,14 @@
       </c>
       <c r="G24" s="149">
         <f t="shared" si="1"/>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H24" s="150">
         <v>4.0999999999999996</v>
       </c>
       <c r="I24" s="151">
         <f t="shared" si="2"/>
-        <v>4.0305</v>
+        <v>4.1264000000000003</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
@@ -5110,12 +5123,12 @@
       </c>
       <c r="G25" s="149">
         <f t="shared" si="1"/>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H25" s="150"/>
       <c r="I25" s="151">
         <f t="shared" si="2"/>
-        <v>1.1604999999999999</v>
+        <v>1.2564000000000002</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
@@ -5130,12 +5143,12 @@
       </c>
       <c r="G26" s="149">
         <f t="shared" si="1"/>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H26" s="150"/>
       <c r="I26" s="151">
         <f t="shared" si="2"/>
-        <v>1.1604999999999999</v>
+        <v>1.2564000000000002</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
@@ -5150,12 +5163,12 @@
       </c>
       <c r="G27" s="149">
         <f t="shared" si="1"/>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H27" s="150"/>
       <c r="I27" s="151">
         <f t="shared" si="2"/>
-        <v>1.1604999999999999</v>
+        <v>1.2564000000000002</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
@@ -5170,12 +5183,12 @@
       </c>
       <c r="G28" s="152">
         <f t="shared" si="1"/>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
       <c r="H28" s="153"/>
       <c r="I28" s="154">
         <f t="shared" si="2"/>
-        <v>1.1604999999999999</v>
+        <v>1.2564000000000002</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
@@ -5188,21 +5201,21 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="169" t="s">
+      <c r="B31" s="182" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="169"/>
-      <c r="D31" s="169"/>
-      <c r="E31" s="169"/>
+      <c r="C31" s="182"/>
+      <c r="D31" s="182"/>
+      <c r="E31" s="182"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="188" t="s">
+      <c r="C32" s="185" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="189"/>
+      <c r="D32" s="186"/>
       <c r="E32" s="7" t="s">
         <v>17</v>
       </c>
@@ -5211,23 +5224,23 @@
       <c r="B33" s="44">
         <v>1</v>
       </c>
-      <c r="C33" s="190" t="s">
+      <c r="C33" s="187" t="s">
         <v>242</v>
       </c>
-      <c r="D33" s="191"/>
+      <c r="D33" s="188"/>
       <c r="E33" s="112">
         <f>IF('1.Tecnica'!I19&gt;0,'1.Tecnica'!I19,"")</f>
-        <v>3.95</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="44">
         <v>2</v>
       </c>
-      <c r="C34" s="186" t="s">
+      <c r="C34" s="183" t="s">
         <v>278</v>
       </c>
-      <c r="D34" s="187"/>
+      <c r="D34" s="184"/>
       <c r="E34" s="112">
         <f>IF('2.ArquitectonicaEstructural'!I95&gt;0,'2.ArquitectonicaEstructural'!I95,"")</f>
         <v>4.4233333333333329</v>
@@ -5237,13 +5250,13 @@
       <c r="B35" s="44">
         <v>3</v>
       </c>
-      <c r="C35" s="186" t="s">
+      <c r="C35" s="183" t="s">
         <v>243</v>
       </c>
-      <c r="D35" s="187"/>
+      <c r="D35" s="184"/>
       <c r="E35" s="112">
         <f>IF('3.Electrica'!I28&gt;0,'3.Electrica'!I28,"")</f>
-        <v>2.5</v>
+        <v>4.166666666666667</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
@@ -5254,19 +5267,19 @@
         <v>277</v>
       </c>
       <c r="D36" s="52"/>
-      <c r="E36" s="112" t="str">
+      <c r="E36" s="112">
         <f>IF('4.Bodegaje'!I23&gt;0,'4.Bodegaje'!I23,"")</f>
-        <v/>
+        <v>3.75</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="44">
         <v>4</v>
       </c>
-      <c r="C37" s="186" t="s">
+      <c r="C37" s="183" t="s">
         <v>244</v>
       </c>
-      <c r="D37" s="187"/>
+      <c r="D37" s="184"/>
       <c r="E37" s="112" t="str">
         <f>IF('5.Planos'!I17&gt;0,'5.Planos'!I17,"")</f>
         <v/>
@@ -5276,10 +5289,10 @@
       <c r="B38" s="45">
         <v>5</v>
       </c>
-      <c r="C38" s="183" t="s">
+      <c r="C38" s="176" t="s">
         <v>245</v>
       </c>
-      <c r="D38" s="184"/>
+      <c r="D38" s="177"/>
       <c r="E38" s="140">
         <f>IF('6.Archivos'!H18&gt;0,'6.Archivos'!H18,"")</f>
         <v>4.6000000000000005</v>
@@ -5291,11 +5304,16 @@
       </c>
       <c r="E39" s="139">
         <f>AVERAGE(E33:E38)</f>
-        <v>3.8683333333333332</v>
+        <v>4.1880000000000006</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B4:D6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E11"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B8:E8"/>
@@ -5308,11 +5326,6 @@
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="B4:D6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B13" r:id="rId1" xr:uid="{483A41C9-7E48-49AD-8086-D82820AFEABB}"/>
@@ -5344,46 +5357,46 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="169" t="s">
+      <c r="B2" s="182" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="191" t="s">
         <v>301</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="170"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
     </row>
     <row r="4" spans="2:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="168"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190"/>
+      <c r="E5" s="190"/>
+      <c r="F5" s="190"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="190"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
@@ -5722,22 +5735,22 @@
       <c r="F2" s="109"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="191" t="s">
         <v>504</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>505</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
     </row>
     <row r="5" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
@@ -5946,24 +5959,24 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>443</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
+      <c r="B5" s="189"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="189"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="189"/>
+      <c r="G5" s="189"/>
+      <c r="H5" s="189"/>
     </row>
     <row r="6" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
@@ -7614,18 +7627,18 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>246</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
+      <c r="B5" s="189"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="189"/>
+      <c r="E5" s="189"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
@@ -7877,11 +7890,11 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H15" s="131" t="s">
-        <v>562</v>
-      </c>
-      <c r="I15" s="164">
-        <v>4.5</v>
+      <c r="H15" s="205" t="s">
+        <v>572</v>
+      </c>
+      <c r="I15" s="61">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -7953,7 +7966,7 @@
       </c>
       <c r="I19" s="31">
         <f>AVERAGE(I7:I18)</f>
-        <v>3.95</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -8001,26 +8014,26 @@
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="168"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190"/>
+      <c r="E5" s="190"/>
+      <c r="F5" s="190"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="190"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
@@ -10392,7 +10405,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
-  <sheetPr filterMode="1"/>
   <dimension ref="B2:K46"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
@@ -10420,26 +10432,26 @@
       </c>
     </row>
     <row r="4" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
     </row>
     <row r="5" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="168"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190"/>
+      <c r="E5" s="190"/>
+      <c r="F5" s="190"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="190"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
@@ -10527,11 +10539,11 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H9" s="137" t="s">
-        <v>568</v>
-      </c>
-      <c r="I9" s="111">
-        <v>0</v>
+      <c r="H9" s="160" t="s">
+        <v>573</v>
+      </c>
+      <c r="I9" s="157">
+        <v>5</v>
       </c>
       <c r="K9" s="166" t="s">
         <v>559</v>
@@ -10593,7 +10605,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="22.8" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:11" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B12" s="27" t="s">
         <v>329</v>
       </c>
@@ -10671,11 +10683,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H14" s="137" t="s">
-        <v>568</v>
-      </c>
-      <c r="I14" s="111">
-        <v>0</v>
+      <c r="H14" s="137"/>
+      <c r="I14" s="157">
+        <v>5</v>
       </c>
       <c r="K14" s="166" t="s">
         <v>559</v>
@@ -10701,11 +10711,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H15" s="137" t="s">
-        <v>568</v>
-      </c>
-      <c r="I15" s="111">
-        <v>0</v>
+      <c r="H15" s="137"/>
+      <c r="I15" s="157">
+        <v>5</v>
       </c>
       <c r="K15" s="166" t="s">
         <v>559</v>
@@ -10731,11 +10739,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H16" s="137" t="s">
-        <v>568</v>
-      </c>
-      <c r="I16" s="111">
-        <v>0</v>
+      <c r="H16" s="137"/>
+      <c r="I16" s="157">
+        <v>5</v>
       </c>
       <c r="K16" s="166" t="s">
         <v>559</v>
@@ -10797,7 +10803,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="34.200000000000003" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:11" ht="34.200000000000003" x14ac:dyDescent="0.4">
       <c r="B19" s="27" t="s">
         <v>313</v>
       </c>
@@ -10883,7 +10889,7 @@
       <c r="H22" s="47"/>
       <c r="I22" s="162"/>
     </row>
-    <row r="23" spans="2:11" ht="34.200000000000003" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:11" ht="34.200000000000003" x14ac:dyDescent="0.4">
       <c r="B23" s="16" t="s">
         <v>184</v>
       </c>
@@ -10912,7 +10918,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="24" spans="2:11" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B24" s="16" t="s">
         <v>186</v>
       </c>
@@ -10940,7 +10946,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="25" spans="2:11" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B25" s="16" t="s">
         <v>185</v>
       </c>
@@ -10968,7 +10974,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="45.6" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:11" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B26" s="16" t="s">
         <v>188</v>
       </c>
@@ -11010,13 +11016,13 @@
       <c r="H27" s="25"/>
       <c r="I27" s="163"/>
     </row>
-    <row r="28" spans="2:11" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.4">
       <c r="H28" s="42" t="s">
         <v>248</v>
       </c>
       <c r="I28" s="49">
         <f>AVERAGE(I7:I27)</f>
-        <v>2.5</v>
+        <v>4.166666666666667</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.4">
@@ -11152,11 +11158,6 @@
   </sheetData>
   <autoFilter ref="B6:I35" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
     <filterColumn colId="4" showButton="0"/>
-    <filterColumn colId="7">
-      <filters blank="1">
-        <filter val="0"/>
-      </filters>
-    </filterColumn>
   </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="B4:I5"/>
@@ -11196,26 +11197,26 @@
       </c>
     </row>
     <row r="4" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B5" s="168"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190"/>
+      <c r="E5" s="190"/>
+      <c r="F5" s="190"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="190"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
@@ -11273,11 +11274,9 @@
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H8" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I8" s="111">
-        <v>0</v>
+      <c r="H8" s="137"/>
+      <c r="I8" s="157">
+        <v>5</v>
       </c>
       <c r="K8" s="166" t="s">
         <v>559</v>
@@ -11303,11 +11302,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H9" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I9" s="111">
-        <v>0</v>
+      <c r="H9" s="137"/>
+      <c r="I9" s="157">
+        <v>5</v>
       </c>
       <c r="K9" s="166" t="s">
         <v>559</v>
@@ -11333,11 +11330,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H10" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I10" s="111">
-        <v>0</v>
+      <c r="H10" s="137"/>
+      <c r="I10" s="157">
+        <v>5</v>
       </c>
       <c r="K10" s="166" t="s">
         <v>559</v>
@@ -11363,11 +11358,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H11" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I11" s="111">
-        <v>0</v>
+      <c r="H11" s="137"/>
+      <c r="I11" s="157">
+        <v>5</v>
       </c>
       <c r="K11" s="166" t="s">
         <v>559</v>
@@ -11394,11 +11387,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H12" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I12" s="111">
-        <v>0</v>
+      <c r="H12" s="137"/>
+      <c r="I12" s="157">
+        <v>5</v>
       </c>
       <c r="K12" s="166" t="s">
         <v>559</v>
@@ -11424,11 +11415,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H13" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I13" s="111">
-        <v>0</v>
+      <c r="H13" s="137"/>
+      <c r="I13" s="157">
+        <v>5</v>
       </c>
       <c r="K13" s="166" t="s">
         <v>559</v>
@@ -11455,11 +11444,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H14" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I14" s="111">
-        <v>0</v>
+      <c r="H14" s="137"/>
+      <c r="I14" s="157">
+        <v>5</v>
       </c>
       <c r="K14" s="166" t="s">
         <v>559</v>
@@ -11485,11 +11472,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H15" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I15" s="111">
-        <v>0</v>
+      <c r="H15" s="137"/>
+      <c r="I15" s="157">
+        <v>5</v>
       </c>
       <c r="K15" s="166" t="s">
         <v>559</v>
@@ -11516,11 +11501,9 @@
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H16" s="137" t="s">
-        <v>560</v>
-      </c>
-      <c r="I16" s="111">
-        <v>0</v>
+      <c r="H16" s="137"/>
+      <c r="I16" s="157">
+        <v>5</v>
       </c>
       <c r="K16" s="166" t="s">
         <v>559</v>
@@ -11572,7 +11555,7 @@
         <v>Ver</v>
       </c>
       <c r="H19" s="137" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="I19" s="111">
         <v>0</v>
@@ -11602,7 +11585,7 @@
         <v>Ver</v>
       </c>
       <c r="H20" s="137" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="I20" s="111">
         <v>0</v>
@@ -11632,7 +11615,7 @@
         <v>Ver</v>
       </c>
       <c r="H21" s="137" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="I21" s="111">
         <v>0</v>
@@ -11657,7 +11640,7 @@
       </c>
       <c r="I23" s="49">
         <f>AVERAGE(I7:I22)</f>
-        <v>0</v>
+        <v>3.75</v>
       </c>
     </row>
   </sheetData>
@@ -11699,26 +11682,26 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="189" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B5" s="168"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190"/>
+      <c r="E5" s="190"/>
+      <c r="F5" s="190"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="190"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
